--- a/data/trans_orig/KIDM_A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_A_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81609</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86605</t>
+          <t>86608</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177806</t>
+          <t>177357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183943</t>
+          <t>183865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202747</t>
+          <t>202698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209664</t>
+          <t>209129</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>383251</t>
+          <t>382823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392188</t>
+          <t>392127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>49787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>43867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>95580</t>
+          <t>95290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101258</t>
+          <t>101254</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>271214</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>280393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291820</t>
+          <t>290633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>299475</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>566540</t>
+          <t>567436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578173</t>
+          <t>578572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43851</t>
+          <t>43637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87559</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92450</t>
+          <t>92441</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175739</t>
+          <t>176195</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183909</t>
+          <t>183987</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197202</t>
+          <t>197509</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>207683</t>
+          <t>207632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>375825</t>
+          <t>377232</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389954</t>
+          <t>389835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51526</t>
+          <t>51482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57049</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104347</t>
+          <t>104546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>109951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276813</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287302</t>
+          <t>286730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>294876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>305092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>575732</t>
+          <t>576074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>590640</t>
+          <t>591012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3944</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>32669</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59781</t>
+          <t>59133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65159</t>
+          <t>65155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>221588</t>
+          <t>222274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227505</t>
+          <t>227610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209326</t>
+          <t>209412</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434809</t>
+          <t>435016</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442533</t>
+          <t>442500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63136</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66036</t>
+          <t>66672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72956</t>
+          <t>72969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131827</t>
+          <t>131884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138638</t>
+          <t>138609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>314949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321914</t>
+          <t>322012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>314754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323553</t>
+          <t>323568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633479</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>643740</t>
+          <t>644278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>184</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8585</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154229</t>
+          <t>153884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159791</t>
+          <t>159647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>197353</t>
+          <t>198221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203400</t>
+          <t>203384</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355128</t>
+          <t>355149</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>362143</t>
+          <t>362431</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -6233,7 +6233,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36037</t>
+          <t>35537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88415</t>
+          <t>88847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204751</t>
+          <t>204124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210620</t>
+          <t>210561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264586</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272001</t>
+          <t>271983</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>472475</t>
+          <t>471831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>481647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
